--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260910.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260910.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.52%</t>
+          <t>9.62%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.51%</t>
+          <t>9.34%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.99%</t>
+          <t>6.05%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.18%</t>
+          <t>4.21%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>3.95%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.96%</t>
+          <t>3.91%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.76%</t>
         </is>
       </c>
     </row>
@@ -792,51 +792,51 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.12%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>27,829,000</t>
+          <t>132,826,945</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.06%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>132,826,945</t>
+          <t>27,829,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.73%</t>
+          <t>2.74%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
@@ -975,22 +975,22 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>84,590,000</t>
+          <t>99,718,442</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
@@ -1012,24 +1012,24 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.44%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>99,718,442</t>
+          <t>84,590,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.30%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.93%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>191,053,000</t>
+          <t>254,199,845</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>254,199,845</t>
+          <t>191,053,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.87%</t>
+          <t>1.85%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.81%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,652,868,571</t>
+          <t>10,820,832,523</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,793,239,790</t>
+          <t>6,684,039,190</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>-1,236,046,405</t>
+          <t>-580,571,263</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr"/>
